--- a/docentes/Jiménez Nieto Enrique - Estadisticos 20221.xlsx
+++ b/docentes/Jiménez Nieto Enrique - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="67">
   <si>
     <t>Mat</t>
   </si>
@@ -91,90 +91,108 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>LIBRADO</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>GALVEZ</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>OCAÑA</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>AMAYO</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>TLAXCALA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>MONTERROSAS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>ACOSTA</t>
   </si>
   <si>
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>GALVEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>TLAXCALA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>MONTERROSAS</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>AMAYO</t>
-  </si>
-  <si>
-    <t>ACOSTA</t>
-  </si>
-  <si>
     <t>ZEPEDA</t>
   </si>
   <si>
-    <t>LESLIE YAMILET</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>IRVING URIEL</t>
+    <t>CARLOS YAEL</t>
+  </si>
+  <si>
+    <t>DYLAN</t>
+  </si>
+  <si>
+    <t>ABIEL NEFTALI</t>
+  </si>
+  <si>
+    <t>ERICK DE JESUS</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL</t>
   </si>
   <si>
     <t>SURISADAY</t>
   </si>
   <si>
+    <t>OZIEL</t>
+  </si>
+  <si>
     <t>GUILLERMO</t>
   </si>
   <si>
@@ -188,12 +206,6 @@
   </si>
   <si>
     <t>NAOMI</t>
-  </si>
-  <si>
-    <t>CARLOS YAEL</t>
-  </si>
-  <si>
-    <t>DYLAN</t>
   </si>
   <si>
     <t>MIGUEL ANTONIO</t>
@@ -603,10 +615,10 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -615,7 +627,7 @@
         <v>23</v>
       </c>
       <c r="G2">
-        <v>74.19</v>
+        <v>76.67</v>
       </c>
       <c r="H2">
         <v>8.199999999999999</v>
@@ -824,19 +836,22 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="E2">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>63.33</v>
+      </c>
+      <c r="H2">
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -873,16 +888,19 @@
         <v>31</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>31</v>
       </c>
-      <c r="E4">
-        <v>31</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
       <c r="G4">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <v>8.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -942,16 +960,19 @@
         <v>26</v>
       </c>
       <c r="D7">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>80.77</v>
+      </c>
+      <c r="H7">
+        <v>8.1</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1024,22 +1045,22 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G2">
-        <v>74.19</v>
+        <v>63.33</v>
       </c>
       <c r="H2">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1082,16 +1103,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G4">
-        <v>87.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1160,16 +1181,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F7">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G7">
-        <v>69.23</v>
+        <v>80.77</v>
       </c>
       <c r="H7">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1205,7 +1226,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1237,22 +1258,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920417</v>
+        <v>22330051920034</v>
       </c>
       <c r="B2" t="s">
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1260,22 +1281,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920011</v>
+        <v>22330051920035</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1283,22 +1304,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920016</v>
+        <v>22330051920047</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1306,22 +1327,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920321</v>
+        <v>20330051920196</v>
       </c>
       <c r="B5" t="s">
         <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1329,22 +1350,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920112</v>
+        <v>20330051920317</v>
       </c>
       <c r="B6" t="s">
         <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1352,7 +1373,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920299</v>
+        <v>20330051920321</v>
       </c>
       <c r="B7" t="s">
         <v>29</v>
@@ -1361,13 +1382,13 @@
         <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1375,22 +1396,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920308</v>
+        <v>20330051920330</v>
       </c>
       <c r="B8" t="s">
         <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D8" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1398,22 +1419,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920311</v>
+        <v>20330051920112</v>
       </c>
       <c r="B9" t="s">
         <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1421,16 +1442,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920312</v>
+        <v>20330051920299</v>
       </c>
       <c r="B10" t="s">
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
@@ -1444,91 +1465,91 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920034</v>
+        <v>20330051920308</v>
       </c>
       <c r="B11" t="s">
         <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920035</v>
+        <v>20330051920311</v>
       </c>
       <c r="B12" t="s">
         <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920038</v>
+        <v>20330051920312</v>
       </c>
       <c r="B13" t="s">
         <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920302</v>
+        <v>22330051920038</v>
       </c>
       <c r="B14" t="s">
         <v>36</v>
       </c>
       <c r="C14" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="D14" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1536,22 +1557,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920050</v>
+        <v>22330051920302</v>
       </c>
       <c r="B15" t="s">
         <v>37</v>
       </c>
       <c r="C15" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="D15" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1559,24 +1580,47 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
+        <v>20330051920050</v>
+      </c>
+      <c r="B16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" t="s">
+        <v>65</v>
+      </c>
+      <c r="E16" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
         <v>20330051920309</v>
       </c>
-      <c r="B16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16" t="s">
-        <v>62</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" t="s">
+        <v>66</v>
+      </c>
+      <c r="E17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" t="s">
         <v>15</v>
       </c>
-      <c r="G16">
+      <c r="G17">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Jiménez Nieto Enrique - Estadisticos 20221.xlsx
+++ b/docentes/Jiménez Nieto Enrique - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="58">
   <si>
     <t>Mat</t>
   </si>
@@ -97,6 +97,9 @@
     <t>GALVEZ</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>ROBLES</t>
   </si>
   <si>
@@ -106,70 +109,52 @@
     <t>APALE</t>
   </si>
   <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
     <t>OCAÑA</t>
   </si>
   <si>
-    <t>VASQUEZ</t>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>VALENTE</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>AMAYO</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>AMAYO</t>
-  </si>
-  <si>
     <t>MORENO</t>
   </si>
   <si>
-    <t>TLAXCALA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>MONTERROSAS</t>
+    <t>BELLO</t>
+  </si>
+  <si>
+    <t>GAMEZ</t>
+  </si>
+  <si>
+    <t>ACOSTA</t>
   </si>
   <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>ACOSTA</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>ZEPEDA</t>
+    <t>PAZ</t>
   </si>
   <si>
     <t>CARLOS YAEL</t>
@@ -178,6 +163,9 @@
     <t>DYLAN</t>
   </si>
   <si>
+    <t>JORGE IVAN</t>
+  </si>
+  <si>
     <t>ABIEL NEFTALI</t>
   </si>
   <si>
@@ -187,25 +175,13 @@
     <t>JOSE MIGUEL</t>
   </si>
   <si>
-    <t>SURISADAY</t>
-  </si>
-  <si>
     <t>OZIEL</t>
   </si>
   <si>
-    <t>GUILLERMO</t>
-  </si>
-  <si>
-    <t>MARIA MAGDALENA</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
-    <t>DULCE MARIA</t>
-  </si>
-  <si>
-    <t>NAOMI</t>
+    <t>ZURIEL ARTURO</t>
+  </si>
+  <si>
+    <t>ABIUD</t>
   </si>
   <si>
     <t>MIGUEL ANTONIO</t>
@@ -214,10 +190,7 @@
     <t>ABDIEL ARMANDO</t>
   </si>
   <si>
-    <t>YAHIR</t>
-  </si>
-  <si>
-    <t>SAMANTHA</t>
+    <t>GUILLERMO ALEXANDER</t>
   </si>
 </sst>
 </file>
@@ -865,16 +838,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>83.33</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -914,16 +890,19 @@
         <v>30</v>
       </c>
       <c r="D5">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>83.33</v>
+      </c>
+      <c r="H5">
+        <v>8.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -937,16 +916,19 @@
         <v>32</v>
       </c>
       <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
         <v>32</v>
       </c>
-      <c r="E6">
-        <v>32</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
       <c r="G6">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H6">
+        <v>8.5</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -986,16 +968,19 @@
         <v>18</v>
       </c>
       <c r="D8">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>88.89</v>
+      </c>
+      <c r="H8">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1077,16 +1062,16 @@
         <v>5</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>86.11</v>
+        <v>83.33</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1129,16 +1114,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G5">
-        <v>80</v>
+        <v>83.33</v>
       </c>
       <c r="H5">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1155,16 +1140,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G6">
-        <v>78.13</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>8.5</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1207,16 +1192,16 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G8">
-        <v>83.33</v>
+        <v>88.89</v>
       </c>
       <c r="H8">
-        <v>8</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -1226,7 +1211,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1264,10 +1249,10 @@
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1287,10 +1272,10 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1304,16 +1289,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920047</v>
+        <v>22330051920327</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1327,22 +1312,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920196</v>
+        <v>22330051920047</v>
       </c>
       <c r="B5" t="s">
         <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1350,22 +1335,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920317</v>
+        <v>20330051920196</v>
       </c>
       <c r="B6" t="s">
         <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1373,16 +1358,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920321</v>
+        <v>20330051920317</v>
       </c>
       <c r="B7" t="s">
         <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -1402,10 +1387,10 @@
         <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -1419,16 +1404,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920112</v>
+        <v>20330051920058</v>
       </c>
       <c r="B9" t="s">
         <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -1442,22 +1427,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920299</v>
+        <v>20330051920111</v>
       </c>
       <c r="B10" t="s">
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1465,162 +1450,70 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920308</v>
+        <v>22330051920038</v>
       </c>
       <c r="B11" t="s">
         <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920311</v>
+        <v>22330051920302</v>
       </c>
       <c r="B12" t="s">
         <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="D12" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920312</v>
+        <v>22330051920314</v>
       </c>
       <c r="B13" t="s">
         <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D13" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920038</v>
-      </c>
-      <c r="B14" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" t="s">
-        <v>48</v>
-      </c>
-      <c r="D14" t="s">
-        <v>63</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>11</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920302</v>
-      </c>
-      <c r="B15" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" t="s">
-        <v>46</v>
-      </c>
-      <c r="D15" t="s">
-        <v>64</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>20330051920050</v>
-      </c>
-      <c r="B16" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" t="s">
-        <v>49</v>
-      </c>
-      <c r="D16" t="s">
-        <v>65</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>14</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>20330051920309</v>
-      </c>
-      <c r="B17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17" t="s">
-        <v>50</v>
-      </c>
-      <c r="D17" t="s">
-        <v>66</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>15</v>
-      </c>
-      <c r="G17">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Jiménez Nieto Enrique - Estadisticos 20221.xlsx
+++ b/docentes/Jiménez Nieto Enrique - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="55">
   <si>
     <t>Mat</t>
   </si>
@@ -100,7 +100,7 @@
     <t>PEREZ</t>
   </si>
   <si>
-    <t>ROBLES</t>
+    <t>VELAZQUEZ</t>
   </si>
   <si>
     <t>ESTEVEZ</t>
@@ -124,9 +124,6 @@
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
     <t>REYES</t>
   </si>
   <si>
@@ -136,7 +133,7 @@
     <t>CONTRERAS</t>
   </si>
   <si>
-    <t>LOPEZ</t>
+    <t>PAZ</t>
   </si>
   <si>
     <t>MORENO</t>
@@ -154,9 +151,6 @@
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>PAZ</t>
-  </si>
-  <si>
     <t>CARLOS YAEL</t>
   </si>
   <si>
@@ -166,7 +160,7 @@
     <t>JORGE IVAN</t>
   </si>
   <si>
-    <t>ABIEL NEFTALI</t>
+    <t>GUILLERMO ALEXANDER</t>
   </si>
   <si>
     <t>ERICK DE JESUS</t>
@@ -188,9 +182,6 @@
   </si>
   <si>
     <t>ABDIEL ARMANDO</t>
-  </si>
-  <si>
-    <t>GUILLERMO ALEXANDER</t>
   </si>
 </sst>
 </file>
@@ -1211,7 +1202,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1249,10 +1240,10 @@
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1272,10 +1263,10 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1295,10 +1286,10 @@
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1312,22 +1303,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920047</v>
+        <v>22330051920314</v>
       </c>
       <c r="B5" t="s">
         <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1341,10 +1332,10 @@
         <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
@@ -1367,7 +1358,7 @@
         <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -1390,7 +1381,7 @@
         <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -1410,10 +1401,10 @@
         <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -1433,10 +1424,10 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
@@ -1456,10 +1447,10 @@
         <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1479,10 +1470,10 @@
         <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -1491,29 +1482,6 @@
         <v>12</v>
       </c>
       <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920314</v>
-      </c>
-      <c r="B13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" t="s">
-        <v>57</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Jiménez Nieto Enrique - Estadisticos 20221.xlsx
+++ b/docentes/Jiménez Nieto Enrique - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="49">
   <si>
     <t>Mat</t>
   </si>
@@ -91,9 +91,6 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
     <t>GALVEZ</t>
   </si>
   <si>
@@ -109,24 +106,18 @@
     <t>APALE</t>
   </si>
   <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>VALENTE</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
     <t>OCAÑA</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>VALENTE</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
     <t>AMAYO</t>
   </si>
   <si>
@@ -148,12 +139,6 @@
     <t>ACOSTA</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>CARLOS YAEL</t>
-  </si>
-  <si>
     <t>DYLAN</t>
   </si>
   <si>
@@ -169,19 +154,16 @@
     <t>JOSE MIGUEL</t>
   </si>
   <si>
+    <t>ZURIEL ARTURO</t>
+  </si>
+  <si>
+    <t>ABIUD</t>
+  </si>
+  <si>
+    <t>MIGUEL ANTONIO</t>
+  </si>
+  <si>
     <t>OZIEL</t>
-  </si>
-  <si>
-    <t>ZURIEL ARTURO</t>
-  </si>
-  <si>
-    <t>ABIUD</t>
-  </si>
-  <si>
-    <t>MIGUEL ANTONIO</t>
-  </si>
-  <si>
-    <t>ABDIEL ARMANDO</t>
   </si>
 </sst>
 </file>
@@ -582,10 +564,10 @@
         <v>30</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
         <v>7</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
       </c>
       <c r="F2">
         <v>23</v>
@@ -594,7 +576,7 @@
         <v>76.67</v>
       </c>
       <c r="H2">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -608,10 +590,10 @@
         <v>36</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
         <v>5</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
       </c>
       <c r="F3">
         <v>31</v>
@@ -620,7 +602,7 @@
         <v>86.11</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -803,19 +785,19 @@
         <v>30</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G2">
-        <v>63.33</v>
+        <v>66.67</v>
       </c>
       <c r="H2">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -829,19 +811,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>83.33</v>
+        <v>88.89</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1024,19 +1006,19 @@
         <v>30</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G2">
-        <v>63.33</v>
+        <v>66.67</v>
       </c>
       <c r="H2">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1050,19 +1032,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>83.33</v>
+        <v>88.89</v>
       </c>
       <c r="H3">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1202,7 +1184,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1234,16 +1216,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920034</v>
+        <v>22330051920035</v>
       </c>
       <c r="B2" t="s">
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1257,16 +1239,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920035</v>
+        <v>22330051920327</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1280,22 +1262,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920327</v>
+        <v>22330051920314</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1303,22 +1285,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920314</v>
+        <v>20330051920196</v>
       </c>
       <c r="B5" t="s">
         <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1326,22 +1308,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920196</v>
+        <v>20330051920317</v>
       </c>
       <c r="B6" t="s">
         <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1349,22 +1331,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920317</v>
+        <v>20330051920058</v>
       </c>
       <c r="B7" t="s">
         <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1372,22 +1354,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920330</v>
+        <v>20330051920111</v>
       </c>
       <c r="B8" t="s">
         <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1395,93 +1377,47 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920058</v>
+        <v>22330051920038</v>
       </c>
       <c r="B9" t="s">
         <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920111</v>
+        <v>20330051920330</v>
       </c>
       <c r="B10" t="s">
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="D10" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920038</v>
-      </c>
-      <c r="B11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" t="s">
-        <v>42</v>
-      </c>
-      <c r="D11" t="s">
-        <v>53</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920302</v>
-      </c>
-      <c r="B12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" t="s">
-        <v>54</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Jiménez Nieto Enrique - Estadisticos 20221.xlsx
+++ b/docentes/Jiménez Nieto Enrique - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="52">
   <si>
     <t>Mat</t>
   </si>
@@ -97,6 +97,9 @@
     <t>PEREZ</t>
   </si>
   <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
     <t>VELAZQUEZ</t>
   </si>
   <si>
@@ -124,6 +127,9 @@
     <t>CONTRERAS</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>PAZ</t>
   </si>
   <si>
@@ -143,6 +149,9 @@
   </si>
   <si>
     <t>JORGE IVAN</t>
+  </si>
+  <si>
+    <t>ABIEL NEFTALI</t>
   </si>
   <si>
     <t>GUILLERMO ALEXANDER</t>
@@ -1184,7 +1193,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1222,10 +1231,10 @@
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1245,10 +1254,10 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1262,22 +1271,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920314</v>
+        <v>22330051920047</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1285,22 +1294,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920196</v>
+        <v>22330051920314</v>
       </c>
       <c r="B5" t="s">
         <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1308,22 +1317,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920317</v>
+        <v>20330051920196</v>
       </c>
       <c r="B6" t="s">
         <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1331,22 +1340,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920058</v>
+        <v>20330051920317</v>
       </c>
       <c r="B7" t="s">
         <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1354,16 +1363,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920111</v>
+        <v>20330051920058</v>
       </c>
       <c r="B8" t="s">
         <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -1377,47 +1386,70 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920038</v>
+        <v>20330051920111</v>
       </c>
       <c r="B9" t="s">
         <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920330</v>
+        <v>22330051920038</v>
       </c>
       <c r="B10" t="s">
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>20330051920330</v>
+      </c>
+      <c r="B11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
         <v>17</v>
       </c>
-      <c r="G10">
+      <c r="G11">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Jiménez Nieto Enrique - Estadisticos 20221.xlsx
+++ b/docentes/Jiménez Nieto Enrique - Estadisticos 20221.xlsx
@@ -109,18 +109,18 @@
     <t>APALE</t>
   </si>
   <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>OCAÑA</t>
+  </si>
+  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
     <t>VALENTE</t>
   </si>
   <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>OCAÑA</t>
-  </si>
-  <si>
     <t>AMAYO</t>
   </si>
   <si>
@@ -136,15 +136,15 @@
     <t>MORENO</t>
   </si>
   <si>
+    <t>ACOSTA</t>
+  </si>
+  <si>
     <t>BELLO</t>
   </si>
   <si>
     <t>GAMEZ</t>
   </si>
   <si>
-    <t>ACOSTA</t>
-  </si>
-  <si>
     <t>DYLAN</t>
   </si>
   <si>
@@ -163,16 +163,16 @@
     <t>JOSE MIGUEL</t>
   </si>
   <si>
+    <t>MIGUEL ANTONIO</t>
+  </si>
+  <si>
+    <t>OZIEL</t>
+  </si>
+  <si>
     <t>ZURIEL ARTURO</t>
   </si>
   <si>
     <t>ABIUD</t>
-  </si>
-  <si>
-    <t>MIGUEL ANTONIO</t>
-  </si>
-  <si>
-    <t>OZIEL</t>
   </si>
 </sst>
 </file>
@@ -1363,7 +1363,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920058</v>
+        <v>22330051920038</v>
       </c>
       <c r="B8" t="s">
         <v>30</v>
@@ -1375,24 +1375,24 @@
         <v>48</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920111</v>
+        <v>20330051920330</v>
       </c>
       <c r="B9" t="s">
         <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D9" t="s">
         <v>49</v>
@@ -1401,30 +1401,30 @@
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920038</v>
+        <v>20330051920058</v>
       </c>
       <c r="B10" t="s">
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
         <v>50</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1432,13 +1432,13 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920330</v>
+        <v>20330051920111</v>
       </c>
       <c r="B11" t="s">
         <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
         <v>51</v>
@@ -1447,7 +1447,7 @@
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G11">
         <v>1</v>

--- a/docentes/Jiménez Nieto Enrique - Estadisticos 20221.xlsx
+++ b/docentes/Jiménez Nieto Enrique - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="57">
   <si>
     <t>Mat</t>
   </si>
@@ -91,10 +91,28 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>VALENTE</t>
+  </si>
+  <si>
     <t>GALVEZ</t>
   </si>
   <si>
-    <t>PEREZ</t>
+    <t>HERRERA</t>
   </si>
   <si>
     <t>ROBLES</t>
@@ -103,52 +121,61 @@
     <t>VELAZQUEZ</t>
   </si>
   <si>
+    <t>OCAÑA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>ESTEVEZ</t>
   </si>
   <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>OCAÑA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>VALENTE</t>
+    <t>GAMEZ</t>
   </si>
   <si>
     <t>AMAYO</t>
   </si>
   <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
+    <t>ACOSTA</t>
   </si>
   <si>
     <t>PAZ</t>
   </si>
   <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>ACOSTA</t>
-  </si>
-  <si>
     <t>BELLO</t>
   </si>
   <si>
-    <t>GAMEZ</t>
+    <t>JORGE IVAN</t>
+  </si>
+  <si>
+    <t>FRANCISCO</t>
+  </si>
+  <si>
+    <t>JOSSELIN ANDREA</t>
+  </si>
+  <si>
+    <t>JESUS URIEL</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL</t>
+  </si>
+  <si>
+    <t>ABIUD</t>
   </si>
   <si>
     <t>DYLAN</t>
   </si>
   <si>
-    <t>JORGE IVAN</t>
+    <t>MIGUEL ANTONIO</t>
   </si>
   <si>
     <t>ABIEL NEFTALI</t>
@@ -157,22 +184,10 @@
     <t>GUILLERMO ALEXANDER</t>
   </si>
   <si>
-    <t>ERICK DE JESUS</t>
-  </si>
-  <si>
-    <t>JOSE MIGUEL</t>
-  </si>
-  <si>
-    <t>MIGUEL ANTONIO</t>
-  </si>
-  <si>
     <t>OZIEL</t>
   </si>
   <si>
     <t>ZURIEL ARTURO</t>
-  </si>
-  <si>
-    <t>ABIUD</t>
   </si>
 </sst>
 </file>
@@ -1193,7 +1208,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1225,16 +1240,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920035</v>
+        <v>22330051920327</v>
       </c>
       <c r="B2" t="s">
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1248,22 +1263,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920327</v>
+        <v>22330051920418</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1271,22 +1286,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920047</v>
+        <v>19330051920177</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1294,22 +1309,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920314</v>
+        <v>20330051920259</v>
       </c>
       <c r="B5" t="s">
         <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1317,22 +1332,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920196</v>
+        <v>20330051920317</v>
       </c>
       <c r="B6" t="s">
         <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1340,22 +1355,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920317</v>
+        <v>20330051920111</v>
       </c>
       <c r="B7" t="s">
         <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1363,16 +1378,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920038</v>
+        <v>22330051920035</v>
       </c>
       <c r="B8" t="s">
         <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1386,22 +1401,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920330</v>
+        <v>22330051920038</v>
       </c>
       <c r="B9" t="s">
         <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1409,22 +1424,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920058</v>
+        <v>22330051920047</v>
       </c>
       <c r="B10" t="s">
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D10" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1432,24 +1447,70 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920111</v>
+        <v>22330051920314</v>
       </c>
       <c r="B11" t="s">
         <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>20330051920330</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>20330051920058</v>
+      </c>
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" t="s">
         <v>14</v>
       </c>
-      <c r="G11">
+      <c r="G13">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Jiménez Nieto Enrique - Estadisticos 20221.xlsx
+++ b/docentes/Jiménez Nieto Enrique - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="33">
   <si>
     <t>Mat</t>
   </si>
@@ -91,103 +91,31 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
     <t>SANTIAGO</t>
   </si>
   <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>BELLO</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>VALENTE</t>
-  </si>
-  <si>
-    <t>GALVEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>OCAÑA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>GAMEZ</t>
-  </si>
-  <si>
-    <t>AMAYO</t>
-  </si>
-  <si>
-    <t>ACOSTA</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>BELLO</t>
-  </si>
-  <si>
-    <t>JORGE IVAN</t>
-  </si>
-  <si>
     <t>FRANCISCO</t>
   </si>
   <si>
-    <t>JOSSELIN ANDREA</t>
-  </si>
-  <si>
-    <t>JESUS URIEL</t>
-  </si>
-  <si>
-    <t>JOSE MIGUEL</t>
-  </si>
-  <si>
-    <t>ABIUD</t>
-  </si>
-  <si>
-    <t>DYLAN</t>
-  </si>
-  <si>
-    <t>MIGUEL ANTONIO</t>
-  </si>
-  <si>
-    <t>ABIEL NEFTALI</t>
-  </si>
-  <si>
-    <t>GUILLERMO ALEXANDER</t>
-  </si>
-  <si>
-    <t>OZIEL</t>
-  </si>
-  <si>
     <t>ZURIEL ARTURO</t>
+  </si>
+  <si>
+    <t>MARISOL</t>
   </si>
 </sst>
 </file>
@@ -1033,16 +961,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>66.67</v>
+        <v>96.67</v>
       </c>
       <c r="H2">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1059,16 +987,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G3">
-        <v>88.89</v>
+        <v>94.44</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1094,7 +1022,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1111,13 +1039,13 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G5">
-        <v>83.33</v>
+        <v>86.67</v>
       </c>
       <c r="H5">
         <v>7.8</v>
@@ -1137,16 +1065,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G6">
-        <v>100</v>
+        <v>96.88</v>
       </c>
       <c r="H6">
-        <v>9.300000000000001</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1163,16 +1091,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G7">
-        <v>80.77</v>
+        <v>100</v>
       </c>
       <c r="H7">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1189,16 +1117,16 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G8">
-        <v>88.89</v>
+        <v>100</v>
       </c>
       <c r="H8">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -1208,7 +1136,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1240,22 +1168,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920327</v>
+        <v>22330051920418</v>
       </c>
       <c r="B2" t="s">
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1263,254 +1191,47 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920418</v>
+        <v>20330051920058</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920177</v>
+        <v>20330051920308</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>20330051920259</v>
-      </c>
-      <c r="B5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" t="s">
-        <v>48</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920317</v>
-      </c>
-      <c r="B6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D6" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920111</v>
-      </c>
-      <c r="B7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920035</v>
-      </c>
-      <c r="B8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D8" t="s">
-        <v>51</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920038</v>
-      </c>
-      <c r="B9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" t="s">
-        <v>52</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920047</v>
-      </c>
-      <c r="B10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" t="s">
-        <v>53</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920314</v>
-      </c>
-      <c r="B11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" t="s">
-        <v>43</v>
-      </c>
-      <c r="D11" t="s">
-        <v>54</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920330</v>
-      </c>
-      <c r="B12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" t="s">
-        <v>35</v>
-      </c>
-      <c r="D12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>17</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920058</v>
-      </c>
-      <c r="B13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" t="s">
-        <v>56</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13">
         <v>1</v>
       </c>
     </row>
